--- a/backend/backend/templates/FinalGradesTemplate.xlsx
+++ b/backend/backend/templates/FinalGradesTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JARED\Documents\CapstoneCodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2B1D43-D6B2-44F5-A467-3969802B6A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50B7D1B-ABCD-4299-9E90-D7D304A833EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DA8563-609A-4A02-BEE6-AB2BA1346020}"/>
   </bookViews>
@@ -262,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -297,30 +297,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -336,72 +335,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1206953</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12246</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>340178</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>117345</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8725D9D1-3E6C-135B-F3B7-AF30FF9D7571}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6677024" y="189139"/>
-          <a:ext cx="1283154" cy="1234492"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,7 +707,7 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="D10" s="25"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="23" t="s">
         <v>5</v>
       </c>
@@ -786,7 +719,7 @@
       <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="D11" s="26"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="24" t="s">
         <v>6</v>
       </c>
@@ -803,21 +736,20 @@
     <row r="15" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E16" s="27"/>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="20" t="s">
@@ -924,6 +856,5 @@
     <mergeCell ref="F16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/backend/templates/FinalGradesTemplate.xlsx
+++ b/backend/backend/templates/FinalGradesTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JARED\Documents\CapstoneCodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50B7D1B-ABCD-4299-9E90-D7D304A833EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703D6B9-BF28-4C5E-898A-74075C48ABAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DA8563-609A-4A02-BEE6-AB2BA1346020}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>First Name</t>
   </si>
@@ -71,22 +71,10 @@
     <t>Section :</t>
   </si>
   <si>
-    <t>G4</t>
-  </si>
-  <si>
     <t>Descriptive Title :</t>
   </si>
   <si>
-    <t>IT411</t>
-  </si>
-  <si>
-    <t>Capstone &amp; Research 2</t>
-  </si>
-  <si>
     <t>Instructor:</t>
-  </si>
-  <si>
-    <t>Mr. Joemarie C. Amparo</t>
   </si>
   <si>
     <t>CS1</t>
@@ -262,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -319,6 +307,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,26 +742,28 @@
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
     </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+    </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="9" t="s">
-        <v>13</v>
-      </c>
+      <c r="D21" s="9"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K21" s="7"/>
-      <c r="L21" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
@@ -779,14 +772,9 @@
         <v>10</v>
       </c>
       <c r="C22" s="21"/>
-      <c r="D22" s="10" t="s">
-        <v>11</v>
-      </c>
+      <c r="D22" s="10"/>
       <c r="J22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -803,31 +791,31 @@
         <v>1</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="M28" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="N28" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
@@ -846,7 +834,7 @@
       <c r="N29" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="C2:K2"/>
@@ -854,6 +842,7 @@
     <mergeCell ref="E11:K11"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
